--- a/medical_surveys_questionnaires/039_medical_simulation_training_evaluation_form--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/039_medical_simulation_training_evaluation_form--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Training Session</t>
+          <t>What was the training session about?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>medical_survey</t>
+          <t>medical_survey_results</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Medical Survey</t>
+          <t>Did you take the medical survey?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Simulation Type</t>
+          <t>What type of simulation were you trained on?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Training Date</t>
+          <t>What was the date of the training session?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>training_time</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>What time did the training take place?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>medical_survey</t>
+          <t>training_location</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Medical Survey</t>
+          <t>Where was the training held?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>evaluation</t>
+          <t>medical_survey_results_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Evaluation</t>
+          <t>What were the results of the medical survey?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>evaluation_outcome</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>How would you evaluate the training outcome?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>evaluation_comments</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Were any comments provided for the training session?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>training_location</t>
+          <t>assigned_tool</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Training Location</t>
+          <t>What tool was assigned to you for the training?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>training_outcome</t>
+          <t>evaluation_score</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Training Outcome</t>
+          <t>Evaluation score out of 5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>evaluation_comments</t>
+          <t>training_outcome</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Evaluation Comments</t>
+          <t>How would you evaluate the training outcome of the session?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>medical_survey</t>
+          <t>evaluation_comments_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Medical Survey</t>
+          <t>Were any comments made on the medical survey?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>evaluation_score</t>
+          <t>medical_survey_results_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Evaluation Score</t>
+          <t>Did the medical survey indicate a yes or no response?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>evaluation_comments</t>
+          <t>evaluation_score_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Evaluation Comments</t>
+          <t>What was the evaluation score for the training session?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>medical_survey</t>
+          <t>training_outcome_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Medical Survey</t>
+          <t>Training Outcome 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>training_location</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Training Location</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>training_outcome</t>
+          <t>simulation_type_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Training Outcome</t>
+          <t>What type of simulation was the training based on?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,17 +929,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>evaluation_comments</t>
+          <t>training_date_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Evaluation Comments</t>
+          <t>When was the training session held?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -952,17 +952,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>medical_survey</t>
+          <t>training_time_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Medical Survey</t>
+          <t>Training Time 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>evaluation_score</t>
+          <t>assigned_tool_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Evaluation Score</t>
+          <t>What tool was assigned to you?</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -998,17 +998,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>training_outcome</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Training Outcome</t>
+          <t>Were any comments made on the training?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1021,17 +1021,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>medical_survey</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Medical Survey</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>medical_survey</t>
+          <t>evaluation_score_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Medical Survey</t>
+          <t>Evaluation Score</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>simulation_type</t>
+          <t>training_outcome_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Simulation Type</t>
+          <t>Training Outcome</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1090,67 +1090,21 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>training_date</t>
+          <t>comments_3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Training Date</t>
+          <t>Comments 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Assigned Tool</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1167,10 +1121,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1195,7 +1149,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>medical_survey_choices</t>
+          <t>medical_survey_results_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1212,7 +1166,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>medical_survey_choices</t>
+          <t>medical_survey_results_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1234,12 +1188,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1251,12 +1205,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1268,19 +1222,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>medical_survey_choices</t>
+          <t>medical_survey_results_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1297,7 +1251,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>medical_survey_choices</t>
+          <t>medical_survey_results_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1314,7 +1268,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>evaluation_choices</t>
+          <t>evaluation_outcome_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1331,7 +1285,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>evaluation_choices</t>
+          <t>evaluation_outcome_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1399,7 +1353,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>training_outcome_choices</t>
+          <t>evaluation_score_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1416,7 +1370,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>training_outcome_choices</t>
+          <t>evaluation_score_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1433,313 +1387,313 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>medical_survey_choices</t>
+          <t>evaluation_score_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>medical_survey_choices</t>
+          <t>training_outcome_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>evaluation_score_choices</t>
+          <t>training_outcome_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>evaluation_score_choices</t>
+          <t>medical_survey_results_3_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>evaluation_score_choices</t>
+          <t>medical_survey_results_3_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>evaluation_score_choices</t>
+          <t>evaluation_score_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>evaluation_score_choices</t>
+          <t>evaluation_score_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>medical_survey_choices</t>
+          <t>evaluation_score_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>medical_survey_choices</t>
+          <t>training_outcome_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>training_outcome_choices</t>
+          <t>training_outcome_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>training_outcome_choices</t>
+          <t>simulation_type_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>medical_survey_choices</t>
+          <t>simulation_type_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>medical_survey_choices</t>
+          <t>simulation_type_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>evaluation_score_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>evaluation_score_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>tool1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>tool1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>evaluation_score_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>tool2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>tool2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>evaluation_score_choices</t>
+          <t>medical_survey_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>evaluation_score_choices</t>
+          <t>medical_survey_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>training_outcome_choices</t>
+          <t>evaluation_score_3_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1756,7 +1710,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>training_outcome_choices</t>
+          <t>evaluation_score_3_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1773,136 +1727,51 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>medical_survey_choices</t>
+          <t>evaluation_score_3_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>medical_survey_choices</t>
+          <t>training_outcome_3_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>simulation_type_choices</t>
+          <t>training_outcome_3_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>simulation_type_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>simulation_type_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>assigned_tool_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>chatjimmy</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>chatjimmy</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>assigned_tool_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>tool1</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>tool1</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>assigned_tool_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>tool2</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>tool2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
